--- a/data/station_openings.xlsx
+++ b/data/station_openings.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/baarthur/projects/greg/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/baarthur/ipea/aop/git_baarthur/transit_expansion_employment_sp/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52A5AD8C-804B-B040-B21A-31AC098ECAFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EED0304-8F55-304F-9EF7-022595D43619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="16820" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="to-do" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">data!$A$1:$O$406</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">data!$A$1:$O$405</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="451">
   <si>
     <t>name_line</t>
   </si>
@@ -2162,7 +2162,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O406"/>
+  <dimension ref="A1:O405"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="23.1640625" customWidth="1"/>
@@ -2867,16 +2867,16 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C34" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D34">
         <v>1</v>
       </c>
       <c r="E34">
-        <v>1974</v>
+        <v>1998</v>
       </c>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
@@ -2886,10 +2886,10 @@
         <v>42</v>
       </c>
       <c r="B35">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -2905,10 +2905,10 @@
         <v>42</v>
       </c>
       <c r="B36">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C36" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -2924,16 +2924,16 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D37">
         <v>1</v>
       </c>
       <c r="E37">
-        <v>1998</v>
+        <v>1975</v>
       </c>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
@@ -2943,10 +2943,10 @@
         <v>42</v>
       </c>
       <c r="B38">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -2962,10 +2962,10 @@
         <v>42</v>
       </c>
       <c r="B39">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C39" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -2981,10 +2981,10 @@
         <v>42</v>
       </c>
       <c r="B40">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C40" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -3000,10 +3000,10 @@
         <v>42</v>
       </c>
       <c r="B41">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C41" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -3019,10 +3019,10 @@
         <v>42</v>
       </c>
       <c r="B42">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C42" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -3038,10 +3038,10 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C43" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -3057,16 +3057,19 @@
         <v>42</v>
       </c>
       <c r="B44">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C44" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="D44">
         <v>1</v>
       </c>
       <c r="E44">
-        <v>1975</v>
+        <v>1978</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
       </c>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
@@ -3076,19 +3079,16 @@
         <v>42</v>
       </c>
       <c r="B45">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C45" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="D45">
         <v>1</v>
       </c>
       <c r="E45">
-        <v>1978</v>
-      </c>
-      <c r="F45">
-        <v>1</v>
+        <v>1975</v>
       </c>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
@@ -3098,10 +3098,10 @@
         <v>42</v>
       </c>
       <c r="B46">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C46" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -3117,10 +3117,10 @@
         <v>42</v>
       </c>
       <c r="B47">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C47" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -3136,10 +3136,10 @@
         <v>42</v>
       </c>
       <c r="B48">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C48" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -3155,10 +3155,10 @@
         <v>42</v>
       </c>
       <c r="B49">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C49" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -3174,16 +3174,16 @@
         <v>42</v>
       </c>
       <c r="B50">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C50" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D50">
         <v>1</v>
       </c>
       <c r="E50">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
@@ -3193,10 +3193,10 @@
         <v>42</v>
       </c>
       <c r="B51">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C51" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -3212,10 +3212,10 @@
         <v>42</v>
       </c>
       <c r="B52">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C52" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -3231,10 +3231,10 @@
         <v>42</v>
       </c>
       <c r="B53">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C53" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -3250,10 +3250,10 @@
         <v>42</v>
       </c>
       <c r="B54">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C54" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -3269,10 +3269,10 @@
         <v>42</v>
       </c>
       <c r="B55">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C55" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -3288,10 +3288,10 @@
         <v>42</v>
       </c>
       <c r="B56">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C56" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -3304,32 +3304,42 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="B57">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C57" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D57">
         <v>1</v>
       </c>
       <c r="E57">
-        <v>1974</v>
-      </c>
-      <c r="I57" s="2"/>
-      <c r="J57" s="2"/>
+        <v>2014</v>
+      </c>
+      <c r="I57" s="2">
+        <v>41881</v>
+      </c>
+      <c r="J57" s="2">
+        <v>42669</v>
+      </c>
+      <c r="K57" t="s">
+        <v>389</v>
+      </c>
+      <c r="L57" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>63</v>
       </c>
       <c r="B58">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C58" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -3355,22 +3365,22 @@
         <v>63</v>
       </c>
       <c r="B59">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C59" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="D59">
         <v>1</v>
       </c>
       <c r="E59">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="I59" s="2">
-        <v>41881</v>
+        <v>43196</v>
       </c>
       <c r="J59" s="2">
-        <v>42669</v>
+        <v>43477</v>
       </c>
       <c r="K59" t="s">
         <v>389</v>
@@ -3384,10 +3394,10 @@
         <v>63</v>
       </c>
       <c r="B60">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C60" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -3413,10 +3423,10 @@
         <v>63</v>
       </c>
       <c r="B61">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C61" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -3442,10 +3452,10 @@
         <v>63</v>
       </c>
       <c r="B62">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C62" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -3468,42 +3478,32 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63">
         <v>63</v>
       </c>
-      <c r="B63">
-        <v>62</v>
-      </c>
       <c r="C63" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D63">
         <v>1</v>
       </c>
       <c r="E63">
-        <v>2018</v>
-      </c>
-      <c r="I63" s="2">
-        <v>43196</v>
-      </c>
-      <c r="J63" s="2">
-        <v>43477</v>
-      </c>
-      <c r="K63" t="s">
-        <v>389</v>
-      </c>
-      <c r="L63" t="s">
-        <v>389</v>
-      </c>
+        <v>2002</v>
+      </c>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>69</v>
       </c>
       <c r="B64">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C64" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -3519,10 +3519,10 @@
         <v>69</v>
       </c>
       <c r="B65">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C65" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -3538,10 +3538,10 @@
         <v>69</v>
       </c>
       <c r="B66">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C66" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -3557,10 +3557,10 @@
         <v>69</v>
       </c>
       <c r="B67">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C67" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -3576,10 +3576,10 @@
         <v>69</v>
       </c>
       <c r="B68">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C68" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -3595,16 +3595,16 @@
         <v>69</v>
       </c>
       <c r="B69">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C69" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D69">
         <v>1</v>
       </c>
       <c r="E69">
-        <v>2002</v>
+        <v>2014</v>
       </c>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
@@ -3614,16 +3614,16 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C70" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D70">
         <v>1</v>
       </c>
       <c r="E70">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
@@ -3633,10 +3633,10 @@
         <v>69</v>
       </c>
       <c r="B71">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C71" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -3652,10 +3652,10 @@
         <v>69</v>
       </c>
       <c r="B72">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C72" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -3671,16 +3671,16 @@
         <v>69</v>
       </c>
       <c r="B73">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C73" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D73">
         <v>1</v>
       </c>
       <c r="E73">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
@@ -3690,10 +3690,10 @@
         <v>69</v>
       </c>
       <c r="B74">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C74" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -3709,10 +3709,10 @@
         <v>69</v>
       </c>
       <c r="B75">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C75" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -3728,10 +3728,10 @@
         <v>69</v>
       </c>
       <c r="B76">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C76" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -3747,10 +3747,10 @@
         <v>69</v>
       </c>
       <c r="B77">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C77" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -3766,10 +3766,10 @@
         <v>69</v>
       </c>
       <c r="B78">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C78" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -3782,32 +3782,42 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="B79">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C79" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="D79">
         <v>1</v>
       </c>
       <c r="E79">
-        <v>2018</v>
-      </c>
-      <c r="I79" s="2"/>
-      <c r="J79" s="2"/>
+        <v>2011</v>
+      </c>
+      <c r="I79" s="2">
+        <v>40801</v>
+      </c>
+      <c r="J79" s="2">
+        <v>40801</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="L79" s="3" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>84</v>
       </c>
       <c r="B80">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -3833,22 +3843,22 @@
         <v>84</v>
       </c>
       <c r="B81">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C81" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="D81">
         <v>1</v>
       </c>
       <c r="E81">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="I81" s="2">
-        <v>40801</v>
+        <v>40323</v>
       </c>
       <c r="J81" s="2">
-        <v>40801</v>
+        <v>40323</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>384</v>
@@ -3862,10 +3872,10 @@
         <v>84</v>
       </c>
       <c r="B82">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C82" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -3891,22 +3901,25 @@
         <v>84</v>
       </c>
       <c r="B83">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C83" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D83">
         <v>1</v>
       </c>
       <c r="E83">
-        <v>2010</v>
+        <v>2011</v>
+      </c>
+      <c r="F83">
+        <v>1</v>
       </c>
       <c r="I83" s="2">
-        <v>40323</v>
+        <v>40679</v>
       </c>
       <c r="J83" s="2">
-        <v>40323</v>
+        <v>40679</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>384</v>
@@ -3920,10 +3933,10 @@
         <v>84</v>
       </c>
       <c r="B84">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C84" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -3931,14 +3944,11 @@
       <c r="E84">
         <v>2011</v>
       </c>
-      <c r="F84">
-        <v>1</v>
-      </c>
       <c r="I84" s="2">
-        <v>40679</v>
+        <v>40630</v>
       </c>
       <c r="J84" s="2">
-        <v>40679</v>
+        <v>40630</v>
       </c>
       <c r="K84" s="3" t="s">
         <v>384</v>
@@ -3952,27 +3962,27 @@
         <v>84</v>
       </c>
       <c r="B85">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C85" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D85">
         <v>1</v>
       </c>
       <c r="E85">
-        <v>2011</v>
+        <v>2014</v>
+      </c>
+      <c r="F85">
+        <v>1</v>
       </c>
       <c r="I85" s="2">
-        <v>40630</v>
+        <v>41958</v>
       </c>
       <c r="J85" s="2">
-        <v>40630</v>
+        <v>41965</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="L85" s="3" t="s">
         <v>384</v>
       </c>
     </row>
@@ -3981,28 +3991,31 @@
         <v>84</v>
       </c>
       <c r="B86">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C86" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D86">
         <v>1</v>
       </c>
       <c r="E86">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="F86">
         <v>1</v>
       </c>
       <c r="I86" s="2">
-        <v>41958</v>
+        <v>43123</v>
       </c>
       <c r="J86" s="2">
-        <v>41965</v>
+        <v>43134</v>
       </c>
       <c r="K86" s="3" t="s">
         <v>384</v>
+      </c>
+      <c r="L86" s="4" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
@@ -4010,10 +4023,10 @@
         <v>84</v>
       </c>
       <c r="B87">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C87" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -4025,16 +4038,16 @@
         <v>1</v>
       </c>
       <c r="I87" s="2">
-        <v>43123</v>
+        <v>43194</v>
       </c>
       <c r="J87" s="2">
-        <v>43134</v>
+        <v>43209</v>
       </c>
       <c r="K87" s="3" t="s">
         <v>384</v>
       </c>
       <c r="L87" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
@@ -4042,10 +4055,10 @@
         <v>84</v>
       </c>
       <c r="B88">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C88" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -4053,69 +4066,66 @@
       <c r="E88">
         <v>2018</v>
       </c>
-      <c r="F88">
-        <v>1</v>
-      </c>
       <c r="I88" s="2">
-        <v>43194</v>
+        <v>43400</v>
       </c>
       <c r="J88" s="2">
-        <v>43209</v>
+        <v>43414</v>
       </c>
       <c r="K88" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="L88" s="4" t="s">
-        <v>388</v>
+      <c r="L88" s="3" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="B89">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C89" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D89">
         <v>1</v>
       </c>
       <c r="E89">
-        <v>2018</v>
+        <v>2019</v>
+      </c>
+      <c r="F89">
+        <v>1</v>
       </c>
       <c r="I89" s="2">
-        <v>43400</v>
+        <v>43703</v>
       </c>
       <c r="J89" s="2">
-        <v>43414</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>384</v>
+        <v>43836</v>
+      </c>
+      <c r="K89" t="s">
+        <v>389</v>
+      </c>
+      <c r="L89" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B90">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C90" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D90">
         <v>1</v>
       </c>
       <c r="E90">
         <v>2019</v>
-      </c>
-      <c r="F90">
-        <v>1</v>
       </c>
       <c r="I90" s="2">
         <v>43703</v>
@@ -4135,10 +4145,10 @@
         <v>63</v>
       </c>
       <c r="B91">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C91" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -4164,10 +4174,10 @@
         <v>63</v>
       </c>
       <c r="B92">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C92" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -4193,10 +4203,10 @@
         <v>63</v>
       </c>
       <c r="B93">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C93" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -4219,96 +4229,86 @@
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="B94">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C94" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D94">
         <v>1</v>
       </c>
       <c r="E94">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="I94" s="2">
-        <v>43703</v>
+        <v>44540</v>
       </c>
       <c r="J94" s="2">
-        <v>43836</v>
-      </c>
-      <c r="K94" t="s">
-        <v>389</v>
-      </c>
-      <c r="L94" t="s">
-        <v>389</v>
+        <v>44691</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="B95">
-        <v>94</v>
+        <v>3001</v>
       </c>
       <c r="C95" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D95">
         <v>1</v>
       </c>
       <c r="E95">
-        <v>2021</v>
-      </c>
-      <c r="I95" s="2">
-        <v>44540</v>
-      </c>
-      <c r="J95" s="2">
-        <v>44691</v>
-      </c>
-      <c r="K95" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="L95" s="3" t="s">
-        <v>384</v>
-      </c>
+        <v>1920</v>
+      </c>
+      <c r="I95" s="2"/>
+      <c r="J95" s="2"/>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B96">
-        <v>3001</v>
+        <v>3002</v>
       </c>
       <c r="C96" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D96">
         <v>1</v>
       </c>
       <c r="E96">
-        <v>1920</v>
+        <v>1875</v>
       </c>
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B97">
-        <v>3002</v>
+        <v>3003</v>
       </c>
       <c r="C97" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D97">
         <v>1</v>
       </c>
       <c r="E97">
-        <v>1875</v>
+        <v>1867</v>
       </c>
       <c r="I97" s="2"/>
       <c r="J97" s="2"/>
@@ -4318,16 +4318,16 @@
         <v>103</v>
       </c>
       <c r="B98">
-        <v>3003</v>
+        <v>3004</v>
       </c>
       <c r="C98" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D98">
         <v>1</v>
       </c>
       <c r="E98">
-        <v>1867</v>
+        <v>1960</v>
       </c>
       <c r="I98" s="2"/>
       <c r="J98" s="2"/>
@@ -4337,54 +4337,54 @@
         <v>103</v>
       </c>
       <c r="B99">
-        <v>3004</v>
+        <v>3005</v>
       </c>
       <c r="C99" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D99">
         <v>1</v>
       </c>
       <c r="E99">
-        <v>1960</v>
+        <v>1885</v>
       </c>
       <c r="I99" s="2"/>
       <c r="J99" s="2"/>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B100">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="C100" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D100">
         <v>1</v>
       </c>
       <c r="E100">
-        <v>1885</v>
+        <v>1875</v>
       </c>
       <c r="I100" s="2"/>
       <c r="J100" s="2"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B101">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="C101" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D101">
         <v>1</v>
       </c>
       <c r="E101">
-        <v>1875</v>
+        <v>1952</v>
       </c>
       <c r="I101" s="2"/>
       <c r="J101" s="2"/>
@@ -4394,16 +4394,16 @@
         <v>99</v>
       </c>
       <c r="B102">
-        <v>3007</v>
+        <v>3008</v>
       </c>
       <c r="C102" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D102">
         <v>1</v>
       </c>
       <c r="E102">
-        <v>1952</v>
+        <v>1885</v>
       </c>
       <c r="I102" s="2"/>
       <c r="J102" s="2"/>
@@ -4413,16 +4413,16 @@
         <v>99</v>
       </c>
       <c r="B103">
-        <v>3008</v>
+        <v>3009</v>
       </c>
       <c r="C103" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D103">
         <v>1</v>
       </c>
       <c r="E103">
-        <v>1885</v>
+        <v>1867</v>
       </c>
       <c r="I103" s="2"/>
       <c r="J103" s="2"/>
@@ -4432,73 +4432,73 @@
         <v>99</v>
       </c>
       <c r="B104">
-        <v>3009</v>
+        <v>3010</v>
       </c>
       <c r="C104" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D104">
         <v>1</v>
       </c>
       <c r="E104">
-        <v>1867</v>
+        <v>1883</v>
       </c>
       <c r="I104" s="2"/>
       <c r="J104" s="2"/>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="B105">
-        <v>3010</v>
+        <v>3011</v>
       </c>
       <c r="C105" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D105">
         <v>1</v>
       </c>
       <c r="E105">
-        <v>1883</v>
+        <v>1926</v>
       </c>
       <c r="I105" s="2"/>
       <c r="J105" s="2"/>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B106">
-        <v>3011</v>
+        <v>3012</v>
       </c>
       <c r="C106" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D106">
         <v>1</v>
       </c>
       <c r="E106">
-        <v>1926</v>
+        <v>1875</v>
       </c>
       <c r="I106" s="2"/>
       <c r="J106" s="2"/>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B107">
-        <v>3012</v>
+        <v>3013</v>
       </c>
       <c r="C107" t="s">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="D107">
         <v>1</v>
       </c>
       <c r="E107">
-        <v>1875</v>
+        <v>1947</v>
       </c>
       <c r="I107" s="2"/>
       <c r="J107" s="2"/>
@@ -4508,35 +4508,35 @@
         <v>99</v>
       </c>
       <c r="B108">
-        <v>3013</v>
+        <v>3014</v>
       </c>
       <c r="C108" t="s">
-        <v>40</v>
+        <v>115</v>
       </c>
       <c r="D108">
         <v>1</v>
       </c>
       <c r="E108">
-        <v>1947</v>
+        <v>1883</v>
       </c>
       <c r="I108" s="2"/>
       <c r="J108" s="2"/>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B109">
-        <v>3014</v>
+        <v>3015</v>
       </c>
       <c r="C109" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D109">
         <v>1</v>
       </c>
       <c r="E109">
-        <v>1883</v>
+        <v>1891</v>
       </c>
       <c r="I109" s="2"/>
       <c r="J109" s="2"/>
@@ -4546,16 +4546,16 @@
         <v>103</v>
       </c>
       <c r="B110">
-        <v>3015</v>
+        <v>3016</v>
       </c>
       <c r="C110" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D110">
         <v>1</v>
       </c>
       <c r="E110">
-        <v>1891</v>
+        <v>1955</v>
       </c>
       <c r="I110" s="2"/>
       <c r="J110" s="2"/>
@@ -4565,44 +4565,54 @@
         <v>103</v>
       </c>
       <c r="B111">
-        <v>3016</v>
+        <v>3017</v>
       </c>
       <c r="C111" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D111">
         <v>1</v>
       </c>
       <c r="E111">
-        <v>1955</v>
-      </c>
-      <c r="I111" s="2"/>
-      <c r="J111" s="2"/>
+        <v>2013</v>
+      </c>
+      <c r="F111">
+        <v>1</v>
+      </c>
+      <c r="I111" s="2">
+        <v>41526</v>
+      </c>
+      <c r="J111" s="2">
+        <v>41526</v>
+      </c>
+      <c r="K111" t="s">
+        <v>384</v>
+      </c>
+      <c r="L111" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="B112">
-        <v>3017</v>
+        <v>3018</v>
       </c>
       <c r="C112" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D112">
         <v>1</v>
       </c>
       <c r="E112">
-        <v>2013</v>
-      </c>
-      <c r="F112">
-        <v>1</v>
+        <v>2018</v>
       </c>
       <c r="I112" s="2">
-        <v>41526</v>
+        <v>43190</v>
       </c>
       <c r="J112" s="2">
-        <v>41526</v>
+        <v>43255</v>
       </c>
       <c r="K112" t="s">
         <v>384</v>
@@ -4613,99 +4623,89 @@
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B113">
-        <v>3018</v>
+        <v>3019</v>
       </c>
       <c r="C113" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D113">
         <v>1</v>
       </c>
       <c r="E113">
-        <v>2018</v>
-      </c>
-      <c r="I113" s="2">
-        <v>43190</v>
-      </c>
-      <c r="J113" s="2">
-        <v>43255</v>
-      </c>
-      <c r="K113" t="s">
-        <v>384</v>
-      </c>
-      <c r="L113" t="s">
-        <v>384</v>
-      </c>
+        <v>1987</v>
+      </c>
+      <c r="I113" s="2"/>
+      <c r="J113" s="2"/>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B114">
-        <v>3019</v>
+        <v>3020</v>
       </c>
       <c r="C114" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D114">
         <v>1</v>
       </c>
       <c r="E114">
-        <v>1987</v>
-      </c>
-      <c r="I114" s="2"/>
-      <c r="J114" s="2"/>
+        <v>2021</v>
+      </c>
+      <c r="F114">
+        <v>1</v>
+      </c>
+      <c r="I114" s="2">
+        <v>44506</v>
+      </c>
+      <c r="J114" s="2">
+        <v>44506</v>
+      </c>
+      <c r="K114" t="s">
+        <v>390</v>
+      </c>
+      <c r="L114" t="s">
+        <v>390</v>
+      </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="B115">
-        <v>3020</v>
+        <v>3021</v>
       </c>
       <c r="C115" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D115">
         <v>1</v>
       </c>
       <c r="E115">
-        <v>2021</v>
-      </c>
-      <c r="F115">
-        <v>1</v>
-      </c>
-      <c r="I115" s="2">
-        <v>44506</v>
-      </c>
-      <c r="J115" s="2">
-        <v>44506</v>
-      </c>
-      <c r="K115" t="s">
-        <v>390</v>
-      </c>
-      <c r="L115" t="s">
-        <v>390</v>
-      </c>
+        <v>1886</v>
+      </c>
+      <c r="I115" s="2"/>
+      <c r="J115" s="2"/>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="B116">
-        <v>3021</v>
+        <v>3022</v>
       </c>
       <c r="C116" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D116">
         <v>1</v>
       </c>
       <c r="E116">
-        <v>1886</v>
+        <v>1926</v>
       </c>
       <c r="I116" s="2"/>
       <c r="J116" s="2"/>
@@ -4715,10 +4715,10 @@
         <v>112</v>
       </c>
       <c r="B117">
-        <v>3022</v>
+        <v>3023</v>
       </c>
       <c r="C117" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -4731,58 +4731,58 @@
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B118">
-        <v>3023</v>
+        <v>3024</v>
       </c>
       <c r="C118" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D118">
         <v>1</v>
       </c>
       <c r="E118">
-        <v>1926</v>
-      </c>
-      <c r="I118" s="2"/>
-      <c r="J118" s="2"/>
+        <v>2018</v>
+      </c>
+      <c r="I118" s="2">
+        <v>43190</v>
+      </c>
+      <c r="J118" s="2">
+        <v>43255</v>
+      </c>
+      <c r="K118" t="s">
+        <v>384</v>
+      </c>
+      <c r="L118" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="B119">
-        <v>3024</v>
+        <v>3025</v>
       </c>
       <c r="C119" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D119">
         <v>1</v>
       </c>
       <c r="E119">
-        <v>2018</v>
-      </c>
-      <c r="I119" s="2">
-        <v>43190</v>
-      </c>
-      <c r="J119" s="2">
-        <v>43255</v>
-      </c>
-      <c r="K119" t="s">
-        <v>384</v>
-      </c>
-      <c r="L119" t="s">
-        <v>384</v>
-      </c>
+        <v>1926</v>
+      </c>
+      <c r="I119" s="2"/>
+      <c r="J119" s="2"/>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B120">
-        <v>3025</v>
+        <v>3026</v>
       </c>
       <c r="C120" t="s">
         <v>129</v>
@@ -4798,32 +4798,32 @@
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="B121">
-        <v>3026</v>
+        <v>3027</v>
       </c>
       <c r="C121" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D121">
         <v>1</v>
       </c>
       <c r="E121">
-        <v>1926</v>
+        <v>1867</v>
       </c>
       <c r="I121" s="2"/>
       <c r="J121" s="2"/>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B122">
-        <v>3027</v>
+        <v>3028</v>
       </c>
       <c r="C122" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D122">
         <v>1</v>
@@ -4836,32 +4836,37 @@
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B123">
-        <v>3028</v>
+        <v>3029</v>
       </c>
       <c r="C123" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D123">
         <v>1</v>
       </c>
       <c r="E123">
-        <v>1867</v>
-      </c>
-      <c r="I123" s="2"/>
+        <v>2000</v>
+      </c>
+      <c r="I123" s="2">
+        <v>36673</v>
+      </c>
       <c r="J123" s="2"/>
+      <c r="K123" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>101</v>
       </c>
       <c r="B124">
-        <v>3029</v>
+        <v>3030</v>
       </c>
       <c r="C124" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -4869,23 +4874,18 @@
       <c r="E124">
         <v>2000</v>
       </c>
-      <c r="I124" s="2">
-        <v>36673</v>
-      </c>
+      <c r="I124" s="2"/>
       <c r="J124" s="2"/>
-      <c r="K124" t="s">
-        <v>384</v>
-      </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>101</v>
       </c>
       <c r="B125">
-        <v>3030</v>
+        <v>3031</v>
       </c>
       <c r="C125" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -4898,32 +4898,40 @@
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B126">
-        <v>3031</v>
+        <v>3032</v>
       </c>
       <c r="C126" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D126">
         <v>1</v>
       </c>
       <c r="E126">
-        <v>2000</v>
-      </c>
-      <c r="I126" s="2"/>
+        <v>2008</v>
+      </c>
+      <c r="F126">
+        <v>1</v>
+      </c>
+      <c r="I126" s="2">
+        <v>39596</v>
+      </c>
       <c r="J126" s="2"/>
+      <c r="K126" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>112</v>
       </c>
       <c r="B127">
-        <v>3032</v>
+        <v>3033</v>
       </c>
       <c r="C127" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -4935,7 +4943,7 @@
         <v>1</v>
       </c>
       <c r="I127" s="2">
-        <v>39596</v>
+        <v>39645</v>
       </c>
       <c r="J127" s="2"/>
       <c r="K127" t="s">
@@ -4944,84 +4952,76 @@
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="B128">
-        <v>3033</v>
+        <v>3034</v>
       </c>
       <c r="C128" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D128">
         <v>1</v>
       </c>
       <c r="E128">
-        <v>2008</v>
-      </c>
-      <c r="F128">
-        <v>1</v>
-      </c>
-      <c r="I128" s="2">
-        <v>39645</v>
-      </c>
+        <v>1867</v>
+      </c>
+      <c r="I128" s="2"/>
       <c r="J128" s="2"/>
-      <c r="K128" t="s">
-        <v>384</v>
-      </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B129">
-        <v>3034</v>
+        <v>3035</v>
       </c>
       <c r="C129" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D129">
         <v>1</v>
       </c>
       <c r="E129">
-        <v>1867</v>
+        <v>2000</v>
       </c>
       <c r="I129" s="2"/>
       <c r="J129" s="2"/>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B130">
-        <v>3035</v>
+        <v>3036</v>
       </c>
       <c r="C130" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D130">
         <v>1</v>
       </c>
       <c r="E130">
-        <v>2000</v>
+        <v>1950</v>
       </c>
       <c r="I130" s="2"/>
       <c r="J130" s="2"/>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="B131">
-        <v>3036</v>
+        <v>3037</v>
       </c>
       <c r="C131" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D131">
         <v>1</v>
       </c>
       <c r="E131">
-        <v>1950</v>
+        <v>1955</v>
       </c>
       <c r="I131" s="2"/>
       <c r="J131" s="2"/>
@@ -5031,83 +5031,83 @@
         <v>103</v>
       </c>
       <c r="B132">
-        <v>3037</v>
+        <v>3038</v>
       </c>
       <c r="C132" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D132">
         <v>1</v>
       </c>
       <c r="E132">
-        <v>1955</v>
+        <v>1908</v>
       </c>
       <c r="I132" s="2"/>
       <c r="J132" s="2"/>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B133">
-        <v>3038</v>
+        <v>3039</v>
       </c>
       <c r="C133" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D133">
         <v>1</v>
       </c>
       <c r="E133">
-        <v>1908</v>
+        <v>1929</v>
       </c>
       <c r="I133" s="2"/>
       <c r="J133" s="2"/>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B134">
-        <v>3039</v>
+        <v>3040</v>
       </c>
       <c r="C134" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D134">
         <v>1</v>
       </c>
       <c r="E134">
-        <v>1929</v>
+        <v>1883</v>
       </c>
       <c r="I134" s="2"/>
       <c r="J134" s="2"/>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="B135">
-        <v>3040</v>
+        <v>3041</v>
       </c>
       <c r="C135" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D135">
         <v>1</v>
       </c>
       <c r="E135">
-        <v>1883</v>
+        <v>1895</v>
       </c>
       <c r="I135" s="2"/>
       <c r="J135" s="2"/>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B136">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="C136" t="s">
         <v>144</v>
@@ -5123,76 +5123,76 @@
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="B137">
-        <v>3042</v>
+        <v>3043</v>
       </c>
       <c r="C137" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D137">
         <v>1</v>
       </c>
       <c r="E137">
-        <v>1895</v>
+        <v>1881</v>
       </c>
       <c r="I137" s="2"/>
       <c r="J137" s="2"/>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B138">
-        <v>3043</v>
+        <v>3044</v>
       </c>
       <c r="C138" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D138">
         <v>1</v>
       </c>
       <c r="E138">
-        <v>1881</v>
+        <v>1920</v>
       </c>
       <c r="I138" s="2"/>
       <c r="J138" s="2"/>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="B139">
-        <v>3044</v>
+        <v>3045</v>
       </c>
       <c r="C139" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D139">
         <v>1</v>
       </c>
       <c r="E139">
-        <v>1920</v>
+        <v>1926</v>
       </c>
       <c r="I139" s="2"/>
       <c r="J139" s="2"/>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B140">
-        <v>3045</v>
+        <v>3046</v>
       </c>
       <c r="C140" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D140">
         <v>1</v>
       </c>
       <c r="E140">
-        <v>1926</v>
+        <v>1976</v>
       </c>
       <c r="I140" s="2"/>
       <c r="J140" s="2"/>
@@ -5202,54 +5202,60 @@
         <v>101</v>
       </c>
       <c r="B141">
-        <v>3046</v>
+        <v>3047</v>
       </c>
       <c r="C141" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D141">
         <v>1</v>
       </c>
       <c r="E141">
-        <v>1976</v>
+        <v>1926</v>
       </c>
       <c r="I141" s="2"/>
       <c r="J141" s="2"/>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B142">
-        <v>3047</v>
+        <v>3048</v>
       </c>
       <c r="C142" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D142">
         <v>1</v>
       </c>
       <c r="E142">
-        <v>1926</v>
+        <v>1867</v>
+      </c>
+      <c r="G142">
+        <v>1</v>
       </c>
       <c r="I142" s="2"/>
       <c r="J142" s="2"/>
+      <c r="N142">
+        <v>2010</v>
+      </c>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>103</v>
       </c>
       <c r="B143">
-        <v>3048</v>
+        <v>3049</v>
       </c>
       <c r="C143" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D143">
         <v>1</v>
       </c>
       <c r="E143">
-        <v>1867</v>
+        <v>1888</v>
       </c>
       <c r="G143">
         <v>1</v>
@@ -5257,49 +5263,43 @@
       <c r="I143" s="2"/>
       <c r="J143" s="2"/>
       <c r="N143">
-        <v>2010</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B144">
-        <v>3049</v>
+        <v>3050</v>
       </c>
       <c r="C144" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D144">
         <v>1</v>
       </c>
       <c r="E144">
-        <v>1888</v>
-      </c>
-      <c r="G144">
-        <v>1</v>
+        <v>1983</v>
       </c>
       <c r="I144" s="2"/>
       <c r="J144" s="2"/>
-      <c r="N144">
-        <v>2014</v>
-      </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="B145">
-        <v>3050</v>
+        <v>3051</v>
       </c>
       <c r="C145" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D145">
         <v>1</v>
       </c>
       <c r="E145">
-        <v>1983</v>
+        <v>1957</v>
       </c>
       <c r="I145" s="2"/>
       <c r="J145" s="2"/>
@@ -5309,16 +5309,16 @@
         <v>121</v>
       </c>
       <c r="B146">
-        <v>3051</v>
+        <v>3052</v>
       </c>
       <c r="C146" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D146">
         <v>1</v>
       </c>
       <c r="E146">
-        <v>1957</v>
+        <v>1925</v>
       </c>
       <c r="I146" s="2"/>
       <c r="J146" s="2"/>
@@ -5328,16 +5328,16 @@
         <v>121</v>
       </c>
       <c r="B147">
-        <v>3052</v>
+        <v>3053</v>
       </c>
       <c r="C147" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D147">
         <v>1</v>
       </c>
       <c r="E147">
-        <v>1925</v>
+        <v>1983</v>
       </c>
       <c r="I147" s="2"/>
       <c r="J147" s="2"/>
@@ -5347,10 +5347,10 @@
         <v>121</v>
       </c>
       <c r="B148">
-        <v>3053</v>
+        <v>3054</v>
       </c>
       <c r="C148" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D148">
         <v>1</v>
@@ -5366,16 +5366,16 @@
         <v>121</v>
       </c>
       <c r="B149">
-        <v>3054</v>
+        <v>3055</v>
       </c>
       <c r="C149" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D149">
         <v>1</v>
       </c>
       <c r="E149">
-        <v>1983</v>
+        <v>1938</v>
       </c>
       <c r="I149" s="2"/>
       <c r="J149" s="2"/>
@@ -5385,78 +5385,78 @@
         <v>121</v>
       </c>
       <c r="B150">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="C150" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D150">
         <v>1</v>
       </c>
       <c r="E150">
-        <v>1938</v>
+        <v>1985</v>
       </c>
       <c r="I150" s="2"/>
       <c r="J150" s="2"/>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B151">
-        <v>3056</v>
+        <v>3057</v>
       </c>
       <c r="C151" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D151">
         <v>1</v>
       </c>
       <c r="E151">
-        <v>1985</v>
-      </c>
-      <c r="I151" s="2"/>
+        <v>1986</v>
+      </c>
+      <c r="I151" s="2">
+        <v>31438</v>
+      </c>
       <c r="J151" s="2"/>
+      <c r="K151" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B152">
-        <v>3057</v>
+        <v>3058</v>
       </c>
       <c r="C152" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D152">
         <v>1</v>
       </c>
       <c r="E152">
-        <v>1986</v>
-      </c>
-      <c r="I152" s="2">
-        <v>31438</v>
-      </c>
+        <v>1929</v>
+      </c>
+      <c r="I152" s="2"/>
       <c r="J152" s="2"/>
-      <c r="K152" t="s">
-        <v>384</v>
-      </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>121</v>
       </c>
       <c r="B153">
-        <v>3058</v>
+        <v>3059</v>
       </c>
       <c r="C153" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D153">
         <v>1</v>
       </c>
       <c r="E153">
-        <v>1929</v>
+        <v>1987</v>
       </c>
       <c r="I153" s="2"/>
       <c r="J153" s="2"/>
@@ -5466,78 +5466,78 @@
         <v>121</v>
       </c>
       <c r="B154">
-        <v>3059</v>
+        <v>3060</v>
       </c>
       <c r="C154" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D154">
         <v>1</v>
       </c>
       <c r="E154">
-        <v>1987</v>
+        <v>1979</v>
       </c>
       <c r="I154" s="2"/>
       <c r="J154" s="2"/>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B155">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="C155" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D155">
         <v>1</v>
       </c>
       <c r="E155">
-        <v>1979</v>
-      </c>
-      <c r="I155" s="2"/>
+        <v>1981</v>
+      </c>
+      <c r="I155" s="2">
+        <v>29680</v>
+      </c>
       <c r="J155" s="2"/>
+      <c r="K155" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B156">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="C156" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D156">
         <v>1</v>
       </c>
       <c r="E156">
-        <v>1981</v>
-      </c>
-      <c r="I156" s="2">
-        <v>29680</v>
-      </c>
+        <v>1875</v>
+      </c>
+      <c r="I156" s="2"/>
       <c r="J156" s="2"/>
-      <c r="K156" t="s">
-        <v>384</v>
-      </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B157">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="C157" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D157">
         <v>1</v>
       </c>
       <c r="E157">
-        <v>1875</v>
+        <v>1957</v>
       </c>
       <c r="I157" s="2"/>
       <c r="J157" s="2"/>
@@ -5547,16 +5547,19 @@
         <v>123</v>
       </c>
       <c r="B158">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="C158" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D158">
         <v>1</v>
       </c>
       <c r="E158">
-        <v>1957</v>
+        <v>2000</v>
+      </c>
+      <c r="F158">
+        <v>1</v>
       </c>
       <c r="I158" s="2"/>
       <c r="J158" s="2"/>
@@ -5566,16 +5569,16 @@
         <v>123</v>
       </c>
       <c r="B159">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="C159" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D159">
         <v>1</v>
       </c>
       <c r="E159">
-        <v>2000</v>
+        <v>2007</v>
       </c>
       <c r="F159">
         <v>1</v>
@@ -5588,116 +5591,121 @@
         <v>123</v>
       </c>
       <c r="B160">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="C160" t="s">
-        <v>167</v>
+        <v>87</v>
       </c>
       <c r="D160">
         <v>1</v>
       </c>
       <c r="E160">
-        <v>2007</v>
-      </c>
-      <c r="F160">
-        <v>1</v>
+        <v>1957</v>
       </c>
       <c r="I160" s="2"/>
       <c r="J160" s="2"/>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B161">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="C161" t="s">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="D161">
         <v>1</v>
       </c>
       <c r="E161">
-        <v>1957</v>
+        <v>1979</v>
       </c>
       <c r="I161" s="2"/>
       <c r="J161" s="2"/>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B162">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="C162" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D162">
         <v>1</v>
       </c>
       <c r="E162">
-        <v>1979</v>
-      </c>
-      <c r="I162" s="2"/>
+        <v>2008</v>
+      </c>
+      <c r="F162">
+        <v>1</v>
+      </c>
+      <c r="I162" s="2">
+        <v>39559</v>
+      </c>
       <c r="J162" s="2"/>
+      <c r="K162" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>123</v>
       </c>
       <c r="B163">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="C163" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D163">
         <v>1</v>
       </c>
       <c r="E163">
-        <v>2008</v>
-      </c>
-      <c r="F163">
-        <v>1</v>
-      </c>
-      <c r="I163" s="2">
-        <v>39559</v>
-      </c>
+        <v>1992</v>
+      </c>
+      <c r="I163" s="2"/>
       <c r="J163" s="2"/>
-      <c r="K163" t="s">
-        <v>384</v>
-      </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>123</v>
       </c>
       <c r="B164">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="C164" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D164">
         <v>1</v>
       </c>
       <c r="E164">
-        <v>1992</v>
-      </c>
-      <c r="I164" s="2"/>
+        <v>2000</v>
+      </c>
+      <c r="F164">
+        <v>1</v>
+      </c>
+      <c r="I164" s="2">
+        <v>36691</v>
+      </c>
       <c r="J164" s="2"/>
+      <c r="K164" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>123</v>
       </c>
       <c r="B165">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="C165" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D165">
         <v>1</v>
@@ -5708,29 +5716,24 @@
       <c r="F165">
         <v>1</v>
       </c>
-      <c r="I165" s="2">
-        <v>36691</v>
-      </c>
+      <c r="I165" s="2"/>
       <c r="J165" s="2"/>
-      <c r="K165" t="s">
-        <v>384</v>
-      </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>123</v>
       </c>
       <c r="B166">
-        <v>3071</v>
+        <v>3072</v>
       </c>
       <c r="C166" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D166">
         <v>1</v>
       </c>
       <c r="E166">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="F166">
         <v>1</v>
@@ -5743,16 +5746,16 @@
         <v>123</v>
       </c>
       <c r="B167">
-        <v>3072</v>
+        <v>3073</v>
       </c>
       <c r="C167" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D167">
         <v>1</v>
       </c>
       <c r="E167">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="F167">
         <v>1</v>
@@ -5765,10 +5768,10 @@
         <v>123</v>
       </c>
       <c r="B168">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="C168" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D168">
         <v>1</v>
@@ -5787,10 +5790,10 @@
         <v>123</v>
       </c>
       <c r="B169">
-        <v>3074</v>
+        <v>3075</v>
       </c>
       <c r="C169" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D169">
         <v>1</v>
@@ -5806,22 +5809,19 @@
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B170">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="C170" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D170">
         <v>1</v>
       </c>
       <c r="E170">
-        <v>2000</v>
-      </c>
-      <c r="F170">
-        <v>1</v>
+        <v>1941</v>
       </c>
       <c r="I170" s="2"/>
       <c r="J170" s="2"/>
@@ -5831,16 +5831,16 @@
         <v>121</v>
       </c>
       <c r="B171">
-        <v>3076</v>
+        <v>3077</v>
       </c>
       <c r="C171" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D171">
         <v>1</v>
       </c>
       <c r="E171">
-        <v>1941</v>
+        <v>2011</v>
       </c>
       <c r="I171" s="2"/>
       <c r="J171" s="2"/>
@@ -5850,35 +5850,35 @@
         <v>121</v>
       </c>
       <c r="B172">
-        <v>3077</v>
+        <v>3078</v>
       </c>
       <c r="C172" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D172">
         <v>1</v>
       </c>
       <c r="E172">
-        <v>2011</v>
+        <v>1926</v>
       </c>
       <c r="I172" s="2"/>
       <c r="J172" s="2"/>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B173">
-        <v>3078</v>
+        <v>3079</v>
       </c>
       <c r="C173" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D173">
         <v>1</v>
       </c>
       <c r="E173">
-        <v>1926</v>
+        <v>1981</v>
       </c>
       <c r="I173" s="2"/>
       <c r="J173" s="2"/>
@@ -5888,10 +5888,10 @@
         <v>123</v>
       </c>
       <c r="B174">
-        <v>3079</v>
+        <v>3080</v>
       </c>
       <c r="C174" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D174">
         <v>1</v>
@@ -5904,19 +5904,19 @@
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B175">
-        <v>3080</v>
+        <v>3081</v>
       </c>
       <c r="C175" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D175">
         <v>1</v>
       </c>
       <c r="E175">
-        <v>1981</v>
+        <v>1946</v>
       </c>
       <c r="I175" s="2"/>
       <c r="J175" s="2"/>
@@ -5926,140 +5926,140 @@
         <v>121</v>
       </c>
       <c r="B176">
-        <v>3081</v>
+        <v>3082</v>
       </c>
       <c r="C176" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D176">
         <v>1</v>
       </c>
       <c r="E176">
-        <v>1946</v>
+        <v>1931</v>
       </c>
       <c r="I176" s="2"/>
       <c r="J176" s="2"/>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="B177">
-        <v>3082</v>
+        <v>3083</v>
       </c>
       <c r="C177" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D177">
         <v>1</v>
       </c>
       <c r="E177">
-        <v>1931</v>
+        <v>1914</v>
       </c>
       <c r="I177" s="2"/>
       <c r="J177" s="2"/>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B178">
-        <v>3083</v>
+        <v>3084</v>
       </c>
       <c r="C178" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D178">
         <v>1</v>
       </c>
       <c r="E178">
-        <v>1914</v>
+        <v>1899</v>
       </c>
       <c r="I178" s="2"/>
       <c r="J178" s="2"/>
+      <c r="K178" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="B179">
-        <v>3084</v>
+        <v>3085</v>
       </c>
       <c r="C179" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D179">
         <v>1</v>
       </c>
       <c r="E179">
-        <v>1899</v>
-      </c>
-      <c r="I179" s="2"/>
-      <c r="J179" s="2"/>
+        <v>2014</v>
+      </c>
+      <c r="G179">
+        <v>1</v>
+      </c>
+      <c r="I179" s="2">
+        <v>41732</v>
+      </c>
+      <c r="J179" s="2">
+        <v>41752</v>
+      </c>
       <c r="K179" t="s">
         <v>384</v>
       </c>
+      <c r="L179" t="s">
+        <v>384</v>
+      </c>
+      <c r="M179" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="B180">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="C180" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D180">
         <v>1</v>
       </c>
       <c r="E180">
-        <v>2014</v>
-      </c>
-      <c r="G180">
-        <v>1</v>
-      </c>
-      <c r="I180" s="2">
-        <v>41732</v>
-      </c>
-      <c r="J180" s="2">
-        <v>41752</v>
-      </c>
-      <c r="K180" t="s">
-        <v>384</v>
-      </c>
-      <c r="L180" t="s">
-        <v>384</v>
-      </c>
-      <c r="M180" t="s">
-        <v>391</v>
-      </c>
+        <v>1891</v>
+      </c>
+      <c r="I180" s="2"/>
+      <c r="J180" s="2"/>
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B181">
-        <v>3086</v>
+        <v>3087</v>
       </c>
       <c r="C181" t="s">
-        <v>187</v>
+        <v>52</v>
       </c>
       <c r="D181">
         <v>1</v>
       </c>
       <c r="E181">
-        <v>1891</v>
+        <v>1867</v>
       </c>
       <c r="I181" s="2"/>
       <c r="J181" s="2"/>
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B182">
-        <v>3087</v>
+        <v>3088</v>
       </c>
       <c r="C182" t="s">
         <v>52</v>
@@ -6075,48 +6075,48 @@
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B183">
-        <v>3088</v>
+        <v>3089</v>
       </c>
       <c r="C183" t="s">
-        <v>52</v>
+        <v>188</v>
       </c>
       <c r="D183">
         <v>1</v>
       </c>
       <c r="E183">
-        <v>1867</v>
+        <v>1898</v>
       </c>
       <c r="I183" s="2"/>
       <c r="J183" s="2"/>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="B184">
-        <v>3089</v>
+        <v>3090</v>
       </c>
       <c r="C184" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D184">
         <v>1</v>
       </c>
       <c r="E184">
-        <v>1898</v>
+        <v>1979</v>
       </c>
       <c r="I184" s="2"/>
       <c r="J184" s="2"/>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B185">
-        <v>3090</v>
+        <v>3091</v>
       </c>
       <c r="C185" t="s">
         <v>189</v>
@@ -6132,29 +6132,29 @@
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="B186">
-        <v>3091</v>
+        <v>3092</v>
       </c>
       <c r="C186" t="s">
-        <v>189</v>
+        <v>19</v>
       </c>
       <c r="D186">
         <v>1</v>
       </c>
       <c r="E186">
-        <v>1979</v>
+        <v>1867</v>
       </c>
       <c r="I186" s="2"/>
       <c r="J186" s="2"/>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B187">
-        <v>3092</v>
+        <v>3093</v>
       </c>
       <c r="C187" t="s">
         <v>19</v>
@@ -6170,10 +6170,10 @@
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B188">
-        <v>3093</v>
+        <v>3094</v>
       </c>
       <c r="C188" t="s">
         <v>19</v>
@@ -6189,29 +6189,29 @@
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B189">
-        <v>3094</v>
+        <v>3095</v>
       </c>
       <c r="C189" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D189">
         <v>1</v>
       </c>
       <c r="E189">
-        <v>1867</v>
+        <v>1981</v>
       </c>
       <c r="I189" s="2"/>
       <c r="J189" s="2"/>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B190">
-        <v>3095</v>
+        <v>3096</v>
       </c>
       <c r="C190" t="s">
         <v>16</v>
@@ -6227,110 +6227,115 @@
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B191">
-        <v>3096</v>
+        <v>3097</v>
       </c>
       <c r="C191" t="s">
-        <v>16</v>
+        <v>190</v>
       </c>
       <c r="D191">
         <v>1</v>
       </c>
       <c r="E191">
-        <v>1981</v>
-      </c>
-      <c r="I191" s="2"/>
-      <c r="J191" s="2"/>
+        <v>2014</v>
+      </c>
+      <c r="G191">
+        <v>1</v>
+      </c>
+      <c r="I191" s="2">
+        <v>41732</v>
+      </c>
+      <c r="J191" s="2">
+        <v>41752</v>
+      </c>
+      <c r="K191" t="s">
+        <v>384</v>
+      </c>
+      <c r="L191" t="s">
+        <v>384</v>
+      </c>
+      <c r="N191">
+        <v>1922</v>
+      </c>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="B192">
-        <v>3097</v>
+        <v>3098</v>
       </c>
       <c r="C192" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D192">
         <v>1</v>
       </c>
       <c r="E192">
-        <v>2014</v>
-      </c>
-      <c r="G192">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="I192" s="2">
-        <v>41732</v>
-      </c>
-      <c r="J192" s="2">
-        <v>41752</v>
-      </c>
+        <v>36673</v>
+      </c>
+      <c r="J192" s="2"/>
       <c r="K192" t="s">
         <v>384</v>
       </c>
-      <c r="L192" t="s">
-        <v>384</v>
-      </c>
-      <c r="N192">
-        <v>1922</v>
-      </c>
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B193">
-        <v>3098</v>
+        <v>3099</v>
       </c>
       <c r="C193" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D193">
         <v>1</v>
       </c>
       <c r="E193">
-        <v>2000</v>
-      </c>
-      <c r="I193" s="2">
-        <v>36673</v>
-      </c>
+        <v>2008</v>
+      </c>
+      <c r="F193">
+        <v>1</v>
+      </c>
+      <c r="I193" s="2"/>
       <c r="J193" s="2"/>
-      <c r="K193" t="s">
-        <v>384</v>
-      </c>
     </row>
     <row r="194" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="B194">
-        <v>3099</v>
+        <v>3100</v>
       </c>
       <c r="C194" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D194">
         <v>1</v>
       </c>
       <c r="E194">
-        <v>2008</v>
-      </c>
-      <c r="F194">
-        <v>1</v>
-      </c>
-      <c r="I194" s="2"/>
+        <v>1988</v>
+      </c>
+      <c r="I194" s="2">
+        <v>32494</v>
+      </c>
       <c r="J194" s="2"/>
+      <c r="K194" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="B195">
-        <v>3100</v>
+        <v>3101</v>
       </c>
       <c r="C195" t="s">
         <v>193</v>
@@ -6351,10 +6356,10 @@
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="B196">
-        <v>3101</v>
+        <v>3102</v>
       </c>
       <c r="C196" t="s">
         <v>193</v>
@@ -6375,10 +6380,10 @@
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B197">
-        <v>3102</v>
+        <v>3103</v>
       </c>
       <c r="C197" t="s">
         <v>193</v>
@@ -6399,37 +6404,32 @@
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B198">
-        <v>3103</v>
+        <v>3104</v>
       </c>
       <c r="C198" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D198">
         <v>1</v>
       </c>
       <c r="E198">
-        <v>1988</v>
-      </c>
-      <c r="I198" s="2">
-        <v>32494</v>
-      </c>
+        <v>1926</v>
+      </c>
+      <c r="I198" s="2"/>
       <c r="J198" s="2"/>
-      <c r="K198" t="s">
-        <v>384</v>
-      </c>
     </row>
     <row r="199" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>112</v>
       </c>
       <c r="B199">
-        <v>3104</v>
+        <v>3105</v>
       </c>
       <c r="C199" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D199">
         <v>1</v>
@@ -6442,10 +6442,10 @@
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B200">
-        <v>3105</v>
+        <v>3106</v>
       </c>
       <c r="C200" t="s">
         <v>195</v>
@@ -6454,41 +6454,51 @@
         <v>1</v>
       </c>
       <c r="E200">
-        <v>1926</v>
-      </c>
-      <c r="I200" s="2"/>
-      <c r="J200" s="2"/>
+        <v>2018</v>
+      </c>
+      <c r="I200" s="2">
+        <v>43190</v>
+      </c>
+      <c r="J200" s="2">
+        <v>43255</v>
+      </c>
+      <c r="K200" t="s">
+        <v>384</v>
+      </c>
+      <c r="L200" t="s">
+        <v>384</v>
+      </c>
+      <c r="M200" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="201" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B201">
-        <v>3106</v>
+        <v>3107</v>
       </c>
       <c r="C201" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D201">
         <v>1</v>
       </c>
       <c r="E201">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="I201" s="2">
-        <v>43190</v>
+        <v>44418</v>
       </c>
       <c r="J201" s="2">
-        <v>43255</v>
+        <v>44734</v>
       </c>
       <c r="K201" t="s">
         <v>384</v>
       </c>
       <c r="L201" t="s">
-        <v>384</v>
-      </c>
-      <c r="M201" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="202" spans="1:13" x14ac:dyDescent="0.2">
@@ -6496,39 +6506,39 @@
         <v>123</v>
       </c>
       <c r="B202">
-        <v>3107</v>
+        <v>3108</v>
       </c>
       <c r="C202" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D202">
         <v>1</v>
       </c>
       <c r="E202">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="I202" s="2">
-        <v>44418</v>
+        <v>45684</v>
       </c>
       <c r="J202" s="2">
-        <v>44734</v>
+        <v>45955</v>
       </c>
       <c r="K202" t="s">
         <v>384</v>
       </c>
       <c r="L202" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
     </row>
     <row r="203" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B203">
-        <v>3108</v>
+        <v>3109</v>
       </c>
       <c r="C203" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D203">
         <v>1</v>
@@ -6536,60 +6546,47 @@
       <c r="E203">
         <v>2025</v>
       </c>
+      <c r="F203">
+        <v>1</v>
+      </c>
       <c r="I203" s="2">
-        <v>45684</v>
+        <v>45751</v>
       </c>
       <c r="J203" s="2">
-        <v>45955</v>
+        <v>45751</v>
       </c>
       <c r="K203" t="s">
         <v>384</v>
       </c>
-      <c r="L203" t="s">
-        <v>384</v>
+      <c r="L203" s="5" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="204" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>121</v>
+        <v>63</v>
       </c>
       <c r="B204">
-        <v>3109</v>
+        <v>96</v>
       </c>
       <c r="C204" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D204">
-        <v>1</v>
-      </c>
-      <c r="E204">
-        <v>2025</v>
-      </c>
-      <c r="F204">
-        <v>1</v>
-      </c>
-      <c r="I204" s="2">
-        <v>45751</v>
-      </c>
-      <c r="J204" s="2">
-        <v>45751</v>
-      </c>
-      <c r="K204" t="s">
-        <v>384</v>
-      </c>
-      <c r="L204" s="5" t="s">
-        <v>393</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I204" s="2"/>
+      <c r="J204" s="2"/>
     </row>
     <row r="205" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>63</v>
       </c>
       <c r="B205">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C205" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D205">
         <v>0</v>
@@ -6602,10 +6599,10 @@
         <v>63</v>
       </c>
       <c r="B206">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C206" t="s">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="D206">
         <v>0</v>
@@ -6615,29 +6612,42 @@
     </row>
     <row r="207" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>63</v>
+        <v>201</v>
       </c>
       <c r="B207">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C207" t="s">
-        <v>125</v>
+        <v>202</v>
       </c>
       <c r="D207">
-        <v>0</v>
-      </c>
-      <c r="I207" s="2"/>
-      <c r="J207" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="E207">
+        <v>2026</v>
+      </c>
+      <c r="I207" s="2">
+        <v>46203</v>
+      </c>
+      <c r="J207" s="2">
+        <v>46295</v>
+      </c>
+      <c r="K207" t="s">
+        <v>384</v>
+      </c>
+      <c r="L207" s="5" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="208" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>201</v>
       </c>
       <c r="B208">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C208" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D208">
         <v>1</v>
@@ -6646,7 +6656,7 @@
         <v>2026</v>
       </c>
       <c r="I208" s="2">
-        <v>46203</v>
+        <v>46112</v>
       </c>
       <c r="J208" s="2">
         <v>46295</v>
@@ -6663,10 +6673,10 @@
         <v>201</v>
       </c>
       <c r="B209">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C209" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D209">
         <v>1</v>
@@ -6692,10 +6702,10 @@
         <v>201</v>
       </c>
       <c r="B210">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C210" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="D210">
         <v>1</v>
@@ -6721,10 +6731,10 @@
         <v>201</v>
       </c>
       <c r="B211">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C211" t="s">
-        <v>93</v>
+        <v>205</v>
       </c>
       <c r="D211">
         <v>1</v>
@@ -6750,10 +6760,10 @@
         <v>201</v>
       </c>
       <c r="B212">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C212" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D212">
         <v>1</v>
@@ -6779,10 +6789,10 @@
         <v>201</v>
       </c>
       <c r="B213">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C213" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="D213">
         <v>1</v>
@@ -6808,10 +6818,10 @@
         <v>201</v>
       </c>
       <c r="B214">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C214" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="D214">
         <v>1</v>
@@ -6834,42 +6844,32 @@
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>201</v>
+        <v>27</v>
       </c>
       <c r="B215">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C215" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D215">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E215">
-        <v>2026</v>
-      </c>
-      <c r="I215" s="2">
-        <v>46112</v>
-      </c>
-      <c r="J215" s="2">
-        <v>46295</v>
-      </c>
-      <c r="K215" t="s">
-        <v>384</v>
-      </c>
-      <c r="L215" s="5" t="s">
-        <v>394</v>
-      </c>
+        <v>2027</v>
+      </c>
+      <c r="I215" s="2"/>
+      <c r="J215" s="2"/>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>27</v>
       </c>
       <c r="B216">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C216" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D216">
         <v>0</v>
@@ -6885,10 +6885,10 @@
         <v>27</v>
       </c>
       <c r="B217">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C217" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D217">
         <v>0</v>
@@ -6904,10 +6904,10 @@
         <v>27</v>
       </c>
       <c r="B218">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C218" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D218">
         <v>0</v>
@@ -6923,16 +6923,16 @@
         <v>27</v>
       </c>
       <c r="B219">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C219" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D219">
         <v>0</v>
       </c>
       <c r="E219">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="I219" s="2"/>
       <c r="J219" s="2"/>
@@ -6942,10 +6942,10 @@
         <v>27</v>
       </c>
       <c r="B220">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C220" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D220">
         <v>0</v>
@@ -6961,10 +6961,10 @@
         <v>27</v>
       </c>
       <c r="B221">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C221" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D221">
         <v>0</v>
@@ -6980,10 +6980,10 @@
         <v>27</v>
       </c>
       <c r="B222">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C222" t="s">
-        <v>214</v>
+        <v>14</v>
       </c>
       <c r="D222">
         <v>0</v>
@@ -6996,19 +6996,19 @@
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>27</v>
+        <v>215</v>
       </c>
       <c r="B223">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C223" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="D223">
         <v>0</v>
       </c>
       <c r="E223">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="I223" s="2"/>
       <c r="J223" s="2"/>
@@ -7018,10 +7018,10 @@
         <v>215</v>
       </c>
       <c r="B224">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C224" t="s">
-        <v>55</v>
+        <v>216</v>
       </c>
       <c r="D224">
         <v>0</v>
@@ -7037,10 +7037,10 @@
         <v>215</v>
       </c>
       <c r="B225">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C225" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D225">
         <v>0</v>
@@ -7056,10 +7056,10 @@
         <v>215</v>
       </c>
       <c r="B226">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C226" t="s">
-        <v>217</v>
+        <v>90</v>
       </c>
       <c r="D226">
         <v>0</v>
@@ -7075,10 +7075,10 @@
         <v>215</v>
       </c>
       <c r="B227">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C227" t="s">
-        <v>90</v>
+        <v>218</v>
       </c>
       <c r="D227">
         <v>0</v>
@@ -7094,10 +7094,10 @@
         <v>215</v>
       </c>
       <c r="B228">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C228" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D228">
         <v>0</v>
@@ -7113,18 +7113,20 @@
         <v>215</v>
       </c>
       <c r="B229">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C229" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D229">
         <v>0</v>
       </c>
       <c r="E229">
-        <v>2027</v>
-      </c>
-      <c r="I229" s="2"/>
+        <v>2026</v>
+      </c>
+      <c r="I229" s="2">
+        <v>46204</v>
+      </c>
       <c r="J229" s="2"/>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.2">
@@ -7132,10 +7134,10 @@
         <v>215</v>
       </c>
       <c r="B230">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C230" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D230">
         <v>0</v>
@@ -7153,10 +7155,10 @@
         <v>215</v>
       </c>
       <c r="B231">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C231" t="s">
-        <v>221</v>
+        <v>137</v>
       </c>
       <c r="D231">
         <v>0</v>
@@ -7174,10 +7176,10 @@
         <v>215</v>
       </c>
       <c r="B232">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C232" t="s">
-        <v>137</v>
+        <v>222</v>
       </c>
       <c r="D232">
         <v>0</v>
@@ -7195,10 +7197,10 @@
         <v>215</v>
       </c>
       <c r="B233">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C233" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D233">
         <v>0</v>
@@ -7216,10 +7218,10 @@
         <v>215</v>
       </c>
       <c r="B234">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C234" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D234">
         <v>0</v>
@@ -7237,10 +7239,10 @@
         <v>215</v>
       </c>
       <c r="B235">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C235" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D235">
         <v>0</v>
@@ -7248,9 +7250,7 @@
       <c r="E235">
         <v>2026</v>
       </c>
-      <c r="I235" s="2">
-        <v>46204</v>
-      </c>
+      <c r="I235" s="2"/>
       <c r="J235" s="2"/>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.2">
@@ -7258,10 +7258,10 @@
         <v>215</v>
       </c>
       <c r="B236">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C236" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D236">
         <v>0</v>
@@ -7277,10 +7277,10 @@
         <v>215</v>
       </c>
       <c r="B237">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C237" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D237">
         <v>0</v>
@@ -7293,19 +7293,16 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>215</v>
+        <v>27</v>
       </c>
       <c r="B238">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C238" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D238">
         <v>0</v>
-      </c>
-      <c r="E238">
-        <v>2026</v>
       </c>
       <c r="I238" s="2"/>
       <c r="J238" s="2"/>
@@ -7315,10 +7312,10 @@
         <v>27</v>
       </c>
       <c r="B239">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C239" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D239">
         <v>0</v>
@@ -7331,10 +7328,10 @@
         <v>27</v>
       </c>
       <c r="B240">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C240" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D240">
         <v>0</v>
@@ -7347,10 +7344,10 @@
         <v>27</v>
       </c>
       <c r="B241">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C241" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D241">
         <v>0</v>
@@ -7363,10 +7360,10 @@
         <v>27</v>
       </c>
       <c r="B242">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C242" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D242">
         <v>0</v>
@@ -7379,10 +7376,10 @@
         <v>27</v>
       </c>
       <c r="B243">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C243" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D243">
         <v>0</v>
@@ -7392,29 +7389,27 @@
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="B244">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C244" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D244">
         <v>0</v>
       </c>
-      <c r="I244" s="2"/>
-      <c r="J244" s="2"/>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>84</v>
       </c>
       <c r="B245">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C245" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D245">
         <v>0</v>
@@ -7422,13 +7417,13 @@
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="B246">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C246" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D246">
         <v>0</v>
@@ -7439,10 +7434,10 @@
         <v>69</v>
       </c>
       <c r="B247">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C247" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D247">
         <v>0</v>
@@ -7453,10 +7448,10 @@
         <v>69</v>
       </c>
       <c r="B248">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C248" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D248">
         <v>0</v>
@@ -7467,10 +7462,10 @@
         <v>69</v>
       </c>
       <c r="B249">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C249" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D249">
         <v>0</v>
@@ -7478,16 +7473,31 @@
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B250">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C250" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D250">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E250">
+        <v>2021</v>
+      </c>
+      <c r="I250" s="2">
+        <v>44559</v>
+      </c>
+      <c r="J250" s="2">
+        <v>44623</v>
+      </c>
+      <c r="K250" t="s">
+        <v>384</v>
+      </c>
+      <c r="L250" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.2">
@@ -7495,28 +7505,13 @@
         <v>63</v>
       </c>
       <c r="B251">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C251" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D251">
-        <v>1</v>
-      </c>
-      <c r="E251">
-        <v>2021</v>
-      </c>
-      <c r="I251" s="2">
-        <v>44559</v>
-      </c>
-      <c r="J251" s="2">
-        <v>44623</v>
-      </c>
-      <c r="K251" t="s">
-        <v>384</v>
-      </c>
-      <c r="L251" t="s">
-        <v>439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.2">
@@ -7524,10 +7519,10 @@
         <v>63</v>
       </c>
       <c r="B252">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C252" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D252">
         <v>0</v>
@@ -7538,10 +7533,10 @@
         <v>63</v>
       </c>
       <c r="B253">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C253" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D253">
         <v>0</v>
@@ -7552,10 +7547,10 @@
         <v>63</v>
       </c>
       <c r="B254">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C254" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D254">
         <v>0</v>
@@ -7563,16 +7558,19 @@
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>63</v>
+        <v>201</v>
       </c>
       <c r="B255">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C255" t="s">
-        <v>244</v>
+        <v>62</v>
       </c>
       <c r="D255">
         <v>0</v>
+      </c>
+      <c r="E255">
+        <v>2034</v>
       </c>
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.2">
@@ -7580,10 +7578,10 @@
         <v>201</v>
       </c>
       <c r="B256">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C256" t="s">
-        <v>62</v>
+        <v>245</v>
       </c>
       <c r="D256">
         <v>0</v>
@@ -7597,10 +7595,10 @@
         <v>201</v>
       </c>
       <c r="B257">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C257" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D257">
         <v>0</v>
@@ -7614,10 +7612,10 @@
         <v>201</v>
       </c>
       <c r="B258">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C258" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D258">
         <v>0</v>
@@ -7631,16 +7629,16 @@
         <v>201</v>
       </c>
       <c r="B259">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C259" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D259">
         <v>0</v>
       </c>
       <c r="E259">
-        <v>2034</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.2">
@@ -7648,10 +7646,10 @@
         <v>201</v>
       </c>
       <c r="B260">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C260" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D260">
         <v>0</v>
@@ -7665,10 +7663,10 @@
         <v>201</v>
       </c>
       <c r="B261">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C261" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D261">
         <v>0</v>
@@ -7682,10 +7680,10 @@
         <v>201</v>
       </c>
       <c r="B262">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C262" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D262">
         <v>0</v>
@@ -7699,16 +7697,16 @@
         <v>201</v>
       </c>
       <c r="B263">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C263" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D263">
         <v>0</v>
       </c>
       <c r="E263">
-        <v>2032</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.2">
@@ -7716,10 +7714,10 @@
         <v>201</v>
       </c>
       <c r="B264">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C264" t="s">
-        <v>252</v>
+        <v>92</v>
       </c>
       <c r="D264">
         <v>0</v>
@@ -7730,19 +7728,16 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>201</v>
+        <v>253</v>
       </c>
       <c r="B265">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C265" t="s">
-        <v>92</v>
+        <v>254</v>
       </c>
       <c r="D265">
         <v>0</v>
-      </c>
-      <c r="E265">
-        <v>2034</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.2">
@@ -7750,10 +7745,10 @@
         <v>253</v>
       </c>
       <c r="B266">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C266" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D266">
         <v>0</v>
@@ -7764,10 +7759,10 @@
         <v>253</v>
       </c>
       <c r="B267">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C267" t="s">
-        <v>255</v>
+        <v>53</v>
       </c>
       <c r="D267">
         <v>0</v>
@@ -7778,10 +7773,10 @@
         <v>253</v>
       </c>
       <c r="B268">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C268" t="s">
-        <v>53</v>
+        <v>256</v>
       </c>
       <c r="D268">
         <v>0</v>
@@ -7792,10 +7787,10 @@
         <v>253</v>
       </c>
       <c r="B269">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C269" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D269">
         <v>0</v>
@@ -7806,10 +7801,10 @@
         <v>253</v>
       </c>
       <c r="B270">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C270" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D270">
         <v>0</v>
@@ -7820,10 +7815,10 @@
         <v>253</v>
       </c>
       <c r="B271">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C271" t="s">
-        <v>258</v>
+        <v>233</v>
       </c>
       <c r="D271">
         <v>0</v>
@@ -7834,10 +7829,10 @@
         <v>253</v>
       </c>
       <c r="B272">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C272" t="s">
-        <v>233</v>
+        <v>259</v>
       </c>
       <c r="D272">
         <v>0</v>
@@ -7848,10 +7843,10 @@
         <v>253</v>
       </c>
       <c r="B273">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C273" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D273">
         <v>0</v>
@@ -7862,10 +7857,10 @@
         <v>253</v>
       </c>
       <c r="B274">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C274" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D274">
         <v>0</v>
@@ -7876,10 +7871,10 @@
         <v>253</v>
       </c>
       <c r="B275">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C275" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D275">
         <v>0</v>
@@ -7890,10 +7885,10 @@
         <v>253</v>
       </c>
       <c r="B276">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C276" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D276">
         <v>0</v>
@@ -7904,10 +7899,10 @@
         <v>253</v>
       </c>
       <c r="B277">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C277" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D277">
         <v>0</v>
@@ -7918,10 +7913,10 @@
         <v>253</v>
       </c>
       <c r="B278">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C278" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D278">
         <v>0</v>
@@ -7932,10 +7927,10 @@
         <v>253</v>
       </c>
       <c r="B279">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C279" t="s">
-        <v>265</v>
+        <v>22</v>
       </c>
       <c r="D279">
         <v>0</v>
@@ -7943,13 +7938,13 @@
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="B280">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C280" t="s">
-        <v>22</v>
+        <v>267</v>
       </c>
       <c r="D280">
         <v>0</v>
@@ -7960,10 +7955,10 @@
         <v>266</v>
       </c>
       <c r="B281">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C281" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D281">
         <v>0</v>
@@ -7974,10 +7969,10 @@
         <v>266</v>
       </c>
       <c r="B282">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C282" t="s">
-        <v>268</v>
+        <v>228</v>
       </c>
       <c r="D282">
         <v>0</v>
@@ -7988,10 +7983,10 @@
         <v>266</v>
       </c>
       <c r="B283">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C283" t="s">
-        <v>228</v>
+        <v>269</v>
       </c>
       <c r="D283">
         <v>0</v>
@@ -8002,10 +7997,10 @@
         <v>266</v>
       </c>
       <c r="B284">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C284" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D284">
         <v>0</v>
@@ -8016,10 +8011,10 @@
         <v>266</v>
       </c>
       <c r="B285">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C285" t="s">
-        <v>270</v>
+        <v>89</v>
       </c>
       <c r="D285">
         <v>0</v>
@@ -8030,10 +8025,10 @@
         <v>266</v>
       </c>
       <c r="B286">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C286" t="s">
-        <v>89</v>
+        <v>271</v>
       </c>
       <c r="D286">
         <v>0</v>
@@ -8044,10 +8039,10 @@
         <v>266</v>
       </c>
       <c r="B287">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C287" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D287">
         <v>0</v>
@@ -8058,10 +8053,10 @@
         <v>266</v>
       </c>
       <c r="B288">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C288" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D288">
         <v>0</v>
@@ -8072,10 +8067,10 @@
         <v>266</v>
       </c>
       <c r="B289">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C289" t="s">
-        <v>273</v>
+        <v>81</v>
       </c>
       <c r="D289">
         <v>0</v>
@@ -8086,10 +8081,10 @@
         <v>266</v>
       </c>
       <c r="B290">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C290" t="s">
-        <v>81</v>
+        <v>274</v>
       </c>
       <c r="D290">
         <v>0</v>
@@ -8100,10 +8095,10 @@
         <v>266</v>
       </c>
       <c r="B291">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C291" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D291">
         <v>0</v>
@@ -8114,10 +8109,10 @@
         <v>266</v>
       </c>
       <c r="B292">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C292" t="s">
-        <v>275</v>
+        <v>59</v>
       </c>
       <c r="D292">
         <v>0</v>
@@ -8128,10 +8123,10 @@
         <v>266</v>
       </c>
       <c r="B293">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C293" t="s">
-        <v>59</v>
+        <v>276</v>
       </c>
       <c r="D293">
         <v>0</v>
@@ -8142,10 +8137,10 @@
         <v>266</v>
       </c>
       <c r="B294">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C294" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D294">
         <v>0</v>
@@ -8156,10 +8151,10 @@
         <v>266</v>
       </c>
       <c r="B295">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C295" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D295">
         <v>0</v>
@@ -8170,10 +8165,10 @@
         <v>266</v>
       </c>
       <c r="B296">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C296" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D296">
         <v>0</v>
@@ -8184,10 +8179,10 @@
         <v>266</v>
       </c>
       <c r="B297">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C297" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D297">
         <v>0</v>
@@ -8198,10 +8193,10 @@
         <v>266</v>
       </c>
       <c r="B298">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C298" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D298">
         <v>0</v>
@@ -8212,10 +8207,10 @@
         <v>266</v>
       </c>
       <c r="B299">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C299" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D299">
         <v>0</v>
@@ -8226,10 +8221,10 @@
         <v>266</v>
       </c>
       <c r="B300">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C300" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D300">
         <v>0</v>
@@ -8240,10 +8235,10 @@
         <v>266</v>
       </c>
       <c r="B301">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C301" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D301">
         <v>0</v>
@@ -8254,10 +8249,10 @@
         <v>266</v>
       </c>
       <c r="B302">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C302" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D302">
         <v>0</v>
@@ -8265,13 +8260,13 @@
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
-        <v>266</v>
+        <v>215</v>
       </c>
       <c r="B303">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C303" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D303">
         <v>0</v>
@@ -8282,10 +8277,10 @@
         <v>215</v>
       </c>
       <c r="B304">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C304" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D304">
         <v>0</v>
@@ -8296,10 +8291,10 @@
         <v>215</v>
       </c>
       <c r="B305">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C305" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D305">
         <v>0</v>
@@ -8310,10 +8305,10 @@
         <v>215</v>
       </c>
       <c r="B306">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C306" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D306">
         <v>0</v>
@@ -8324,10 +8319,10 @@
         <v>215</v>
       </c>
       <c r="B307">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C307" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D307">
         <v>0</v>
@@ -8338,10 +8333,10 @@
         <v>215</v>
       </c>
       <c r="B308">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C308" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D308">
         <v>0</v>
@@ -8349,13 +8344,13 @@
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>215</v>
+        <v>292</v>
       </c>
       <c r="B309">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C309" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D309">
         <v>0</v>
@@ -8366,10 +8361,10 @@
         <v>292</v>
       </c>
       <c r="B310">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C310" t="s">
-        <v>293</v>
+        <v>210</v>
       </c>
       <c r="D310">
         <v>0</v>
@@ -8380,10 +8375,10 @@
         <v>292</v>
       </c>
       <c r="B311">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C311" t="s">
-        <v>210</v>
+        <v>35</v>
       </c>
       <c r="D311">
         <v>0</v>
@@ -8394,10 +8389,10 @@
         <v>292</v>
       </c>
       <c r="B312">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C312" t="s">
-        <v>35</v>
+        <v>295</v>
       </c>
       <c r="D312">
         <v>0</v>
@@ -8408,10 +8403,10 @@
         <v>292</v>
       </c>
       <c r="B313">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C313" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D313">
         <v>0</v>
@@ -8422,10 +8417,10 @@
         <v>292</v>
       </c>
       <c r="B314">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C314" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D314">
         <v>0</v>
@@ -8436,10 +8431,10 @@
         <v>292</v>
       </c>
       <c r="B315">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C315" t="s">
-        <v>297</v>
+        <v>270</v>
       </c>
       <c r="D315">
         <v>0</v>
@@ -8450,10 +8445,10 @@
         <v>292</v>
       </c>
       <c r="B316">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C316" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="D316">
         <v>0</v>
@@ -8464,10 +8459,10 @@
         <v>292</v>
       </c>
       <c r="B317">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C317" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="D317">
         <v>0</v>
@@ -8478,10 +8473,10 @@
         <v>292</v>
       </c>
       <c r="B318">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C318" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D318">
         <v>0</v>
@@ -8492,10 +8487,10 @@
         <v>292</v>
       </c>
       <c r="B319">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C319" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D319">
         <v>0</v>
@@ -8506,10 +8501,10 @@
         <v>292</v>
       </c>
       <c r="B320">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C320" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D320">
         <v>0</v>
@@ -8520,10 +8515,10 @@
         <v>292</v>
       </c>
       <c r="B321">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C321" t="s">
-        <v>301</v>
+        <v>91</v>
       </c>
       <c r="D321">
         <v>0</v>
@@ -8534,10 +8529,10 @@
         <v>292</v>
       </c>
       <c r="B322">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C322" t="s">
-        <v>91</v>
+        <v>302</v>
       </c>
       <c r="D322">
         <v>0</v>
@@ -8548,10 +8543,10 @@
         <v>292</v>
       </c>
       <c r="B323">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C323" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D323">
         <v>0</v>
@@ -8562,10 +8557,10 @@
         <v>292</v>
       </c>
       <c r="B324">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C324" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D324">
         <v>0</v>
@@ -8573,13 +8568,13 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="B325">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C325" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D325">
         <v>0</v>
@@ -8590,10 +8585,10 @@
         <v>305</v>
       </c>
       <c r="B326">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C326" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D326">
         <v>0</v>
@@ -8604,10 +8599,10 @@
         <v>305</v>
       </c>
       <c r="B327">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C327" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D327">
         <v>0</v>
@@ -8618,10 +8613,10 @@
         <v>305</v>
       </c>
       <c r="B328">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C328" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D328">
         <v>0</v>
@@ -8632,10 +8627,10 @@
         <v>305</v>
       </c>
       <c r="B329">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C329" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D329">
         <v>0</v>
@@ -8646,10 +8641,10 @@
         <v>305</v>
       </c>
       <c r="B330">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C330" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D330">
         <v>0</v>
@@ -8660,10 +8655,10 @@
         <v>305</v>
       </c>
       <c r="B331">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C331" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D331">
         <v>0</v>
@@ -8674,10 +8669,10 @@
         <v>305</v>
       </c>
       <c r="B332">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C332" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D332">
         <v>0</v>
@@ -8688,10 +8683,10 @@
         <v>305</v>
       </c>
       <c r="B333">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C333" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D333">
         <v>0</v>
@@ -8702,10 +8697,10 @@
         <v>305</v>
       </c>
       <c r="B334">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C334" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D334">
         <v>0</v>
@@ -8716,10 +8711,10 @@
         <v>305</v>
       </c>
       <c r="B335">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C335" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D335">
         <v>0</v>
@@ -8730,10 +8725,10 @@
         <v>305</v>
       </c>
       <c r="B336">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C336" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D336">
         <v>0</v>
@@ -8744,10 +8739,10 @@
         <v>305</v>
       </c>
       <c r="B337">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C337" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D337">
         <v>0</v>
@@ -8758,10 +8753,10 @@
         <v>305</v>
       </c>
       <c r="B338">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C338" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D338">
         <v>0</v>
@@ -8772,10 +8767,10 @@
         <v>305</v>
       </c>
       <c r="B339">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C339" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D339">
         <v>0</v>
@@ -8786,10 +8781,10 @@
         <v>305</v>
       </c>
       <c r="B340">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C340" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D340">
         <v>0</v>
@@ -8800,10 +8795,10 @@
         <v>305</v>
       </c>
       <c r="B341">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C341" t="s">
-        <v>321</v>
+        <v>86</v>
       </c>
       <c r="D341">
         <v>0</v>
@@ -8814,10 +8809,10 @@
         <v>305</v>
       </c>
       <c r="B342">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C342" t="s">
-        <v>86</v>
+        <v>322</v>
       </c>
       <c r="D342">
         <v>0</v>
@@ -8828,10 +8823,10 @@
         <v>305</v>
       </c>
       <c r="B343">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C343" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D343">
         <v>0</v>
@@ -8839,13 +8834,13 @@
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="B344">
-        <v>236</v>
+        <v>6001</v>
       </c>
       <c r="C344" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D344">
         <v>0</v>
@@ -8856,10 +8851,10 @@
         <v>324</v>
       </c>
       <c r="B345">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="C345" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D345">
         <v>0</v>
@@ -8870,10 +8865,10 @@
         <v>324</v>
       </c>
       <c r="B346">
-        <v>6002</v>
+        <v>6003</v>
       </c>
       <c r="C346" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D346">
         <v>0</v>
@@ -8884,10 +8879,10 @@
         <v>324</v>
       </c>
       <c r="B347">
-        <v>6003</v>
+        <v>6004</v>
       </c>
       <c r="C347" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D347">
         <v>0</v>
@@ -8898,10 +8893,10 @@
         <v>324</v>
       </c>
       <c r="B348">
-        <v>6004</v>
+        <v>6005</v>
       </c>
       <c r="C348" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D348">
         <v>0</v>
@@ -8912,10 +8907,10 @@
         <v>324</v>
       </c>
       <c r="B349">
-        <v>6005</v>
+        <v>6006</v>
       </c>
       <c r="C349" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D349">
         <v>0</v>
@@ -8926,10 +8921,10 @@
         <v>324</v>
       </c>
       <c r="B350">
-        <v>6006</v>
+        <v>6007</v>
       </c>
       <c r="C350" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D350">
         <v>0</v>
@@ -8940,10 +8935,10 @@
         <v>324</v>
       </c>
       <c r="B351">
-        <v>6007</v>
+        <v>6008</v>
       </c>
       <c r="C351" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D351">
         <v>0</v>
@@ -8954,10 +8949,10 @@
         <v>324</v>
       </c>
       <c r="B352">
-        <v>6008</v>
+        <v>6009</v>
       </c>
       <c r="C352" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D352">
         <v>0</v>
@@ -8968,10 +8963,10 @@
         <v>324</v>
       </c>
       <c r="B353">
-        <v>6009</v>
+        <v>6010</v>
       </c>
       <c r="C353" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D353">
         <v>0</v>
@@ -8982,10 +8977,10 @@
         <v>324</v>
       </c>
       <c r="B354">
-        <v>6010</v>
+        <v>6011</v>
       </c>
       <c r="C354" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D354">
         <v>0</v>
@@ -8996,10 +8991,10 @@
         <v>324</v>
       </c>
       <c r="B355">
-        <v>6011</v>
+        <v>6012</v>
       </c>
       <c r="C355" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D355">
         <v>0</v>
@@ -9010,10 +9005,10 @@
         <v>324</v>
       </c>
       <c r="B356">
-        <v>6012</v>
+        <v>6013</v>
       </c>
       <c r="C356" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D356">
         <v>0</v>
@@ -9024,10 +9019,10 @@
         <v>324</v>
       </c>
       <c r="B357">
-        <v>6013</v>
+        <v>6014</v>
       </c>
       <c r="C357" t="s">
-        <v>337</v>
+        <v>179</v>
       </c>
       <c r="D357">
         <v>0</v>
@@ -9038,10 +9033,10 @@
         <v>324</v>
       </c>
       <c r="B358">
-        <v>6014</v>
+        <v>6015</v>
       </c>
       <c r="C358" t="s">
-        <v>179</v>
+        <v>338</v>
       </c>
       <c r="D358">
         <v>0</v>
@@ -9052,10 +9047,10 @@
         <v>324</v>
       </c>
       <c r="B359">
-        <v>6015</v>
+        <v>6016</v>
       </c>
       <c r="C359" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D359">
         <v>0</v>
@@ -9066,10 +9061,10 @@
         <v>324</v>
       </c>
       <c r="B360">
-        <v>6016</v>
+        <v>6017</v>
       </c>
       <c r="C360" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D360">
         <v>0</v>
@@ -9080,10 +9075,10 @@
         <v>324</v>
       </c>
       <c r="B361">
-        <v>6017</v>
+        <v>6018</v>
       </c>
       <c r="C361" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D361">
         <v>0</v>
@@ -9094,10 +9089,10 @@
         <v>324</v>
       </c>
       <c r="B362">
-        <v>6018</v>
+        <v>6019</v>
       </c>
       <c r="C362" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D362">
         <v>0</v>
@@ -9108,10 +9103,10 @@
         <v>324</v>
       </c>
       <c r="B363">
-        <v>6019</v>
+        <v>6020</v>
       </c>
       <c r="C363" t="s">
-        <v>342</v>
+        <v>71</v>
       </c>
       <c r="D363">
         <v>0</v>
@@ -9119,13 +9114,13 @@
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>324</v>
+        <v>343</v>
       </c>
       <c r="B364">
-        <v>6020</v>
+        <v>6022</v>
       </c>
       <c r="C364" t="s">
-        <v>71</v>
+        <v>344</v>
       </c>
       <c r="D364">
         <v>0</v>
@@ -9136,10 +9131,10 @@
         <v>343</v>
       </c>
       <c r="B365">
-        <v>6022</v>
+        <v>6023</v>
       </c>
       <c r="C365" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D365">
         <v>0</v>
@@ -9150,10 +9145,10 @@
         <v>343</v>
       </c>
       <c r="B366">
-        <v>6023</v>
+        <v>6024</v>
       </c>
       <c r="C366" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D366">
         <v>0</v>
@@ -9164,10 +9159,10 @@
         <v>343</v>
       </c>
       <c r="B367">
-        <v>6024</v>
+        <v>6025</v>
       </c>
       <c r="C367" t="s">
-        <v>346</v>
+        <v>113</v>
       </c>
       <c r="D367">
         <v>0</v>
@@ -9178,10 +9173,10 @@
         <v>343</v>
       </c>
       <c r="B368">
-        <v>6025</v>
+        <v>6026</v>
       </c>
       <c r="C368" t="s">
-        <v>113</v>
+        <v>347</v>
       </c>
       <c r="D368">
         <v>0</v>
@@ -9192,10 +9187,10 @@
         <v>343</v>
       </c>
       <c r="B369">
-        <v>6026</v>
+        <v>6027</v>
       </c>
       <c r="C369" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D369">
         <v>0</v>
@@ -9206,10 +9201,10 @@
         <v>343</v>
       </c>
       <c r="B370">
-        <v>6027</v>
+        <v>6028</v>
       </c>
       <c r="C370" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D370">
         <v>0</v>
@@ -9220,10 +9215,10 @@
         <v>343</v>
       </c>
       <c r="B371">
-        <v>6028</v>
+        <v>6029</v>
       </c>
       <c r="C371" t="s">
-        <v>349</v>
+        <v>9</v>
       </c>
       <c r="D371">
         <v>0</v>
@@ -9234,10 +9229,10 @@
         <v>343</v>
       </c>
       <c r="B372">
-        <v>6029</v>
+        <v>6030</v>
       </c>
       <c r="C372" t="s">
-        <v>9</v>
+        <v>350</v>
       </c>
       <c r="D372">
         <v>0</v>
@@ -9248,10 +9243,10 @@
         <v>343</v>
       </c>
       <c r="B373">
-        <v>6030</v>
+        <v>6031</v>
       </c>
       <c r="C373" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D373">
         <v>0</v>
@@ -9262,10 +9257,10 @@
         <v>343</v>
       </c>
       <c r="B374">
-        <v>6031</v>
+        <v>6032</v>
       </c>
       <c r="C374" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D374">
         <v>0</v>
@@ -9276,10 +9271,10 @@
         <v>343</v>
       </c>
       <c r="B375">
-        <v>6032</v>
+        <v>6033</v>
       </c>
       <c r="C375" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D375">
         <v>0</v>
@@ -9290,10 +9285,10 @@
         <v>343</v>
       </c>
       <c r="B376">
-        <v>6033</v>
+        <v>6034</v>
       </c>
       <c r="C376" t="s">
-        <v>353</v>
+        <v>96</v>
       </c>
       <c r="D376">
         <v>0</v>
@@ -9304,10 +9299,10 @@
         <v>343</v>
       </c>
       <c r="B377">
-        <v>6034</v>
+        <v>6035</v>
       </c>
       <c r="C377" t="s">
-        <v>96</v>
+        <v>354</v>
       </c>
       <c r="D377">
         <v>0</v>
@@ -9318,10 +9313,10 @@
         <v>343</v>
       </c>
       <c r="B378">
-        <v>6035</v>
+        <v>6036</v>
       </c>
       <c r="C378" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D378">
         <v>0</v>
@@ -9332,10 +9327,10 @@
         <v>343</v>
       </c>
       <c r="B379">
-        <v>6036</v>
+        <v>6037</v>
       </c>
       <c r="C379" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D379">
         <v>0</v>
@@ -9346,10 +9341,10 @@
         <v>343</v>
       </c>
       <c r="B380">
-        <v>6037</v>
+        <v>6038</v>
       </c>
       <c r="C380" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D380">
         <v>0</v>
@@ -9360,10 +9355,10 @@
         <v>343</v>
       </c>
       <c r="B381">
-        <v>6038</v>
+        <v>6039</v>
       </c>
       <c r="C381" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D381">
         <v>0</v>
@@ -9374,10 +9369,10 @@
         <v>343</v>
       </c>
       <c r="B382">
-        <v>6039</v>
+        <v>6040</v>
       </c>
       <c r="C382" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D382">
         <v>0</v>
@@ -9388,10 +9383,10 @@
         <v>343</v>
       </c>
       <c r="B383">
-        <v>6040</v>
+        <v>6041</v>
       </c>
       <c r="C383" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D383">
         <v>0</v>
@@ -9402,10 +9397,10 @@
         <v>343</v>
       </c>
       <c r="B384">
-        <v>6041</v>
+        <v>6042</v>
       </c>
       <c r="C384" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D384">
         <v>0</v>
@@ -9416,10 +9411,10 @@
         <v>343</v>
       </c>
       <c r="B385">
-        <v>6042</v>
+        <v>6043</v>
       </c>
       <c r="C385" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D385">
         <v>0</v>
@@ -9427,27 +9422,30 @@
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
-        <v>343</v>
+        <v>103</v>
       </c>
       <c r="B386">
-        <v>6043</v>
+        <v>6044</v>
       </c>
       <c r="C386" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D386">
         <v>0</v>
+      </c>
+      <c r="F386">
+        <v>1</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B387">
-        <v>6044</v>
+        <v>6045</v>
       </c>
       <c r="C387" t="s">
-        <v>363</v>
+        <v>259</v>
       </c>
       <c r="D387">
         <v>0</v>
@@ -9458,13 +9456,13 @@
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B388">
-        <v>6045</v>
+        <v>6046</v>
       </c>
       <c r="C388" t="s">
-        <v>259</v>
+        <v>14</v>
       </c>
       <c r="D388">
         <v>0</v>
@@ -9478,10 +9476,10 @@
         <v>101</v>
       </c>
       <c r="B389">
-        <v>6046</v>
+        <v>6047</v>
       </c>
       <c r="C389" t="s">
-        <v>14</v>
+        <v>364</v>
       </c>
       <c r="D389">
         <v>0</v>
@@ -9492,13 +9490,13 @@
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B390">
-        <v>6047</v>
+        <v>6048</v>
       </c>
       <c r="C390" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D390">
         <v>0</v>
@@ -9512,10 +9510,10 @@
         <v>112</v>
       </c>
       <c r="B391">
-        <v>6048</v>
+        <v>6049</v>
       </c>
       <c r="C391" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D391">
         <v>0</v>
@@ -9526,19 +9524,16 @@
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B392">
-        <v>6049</v>
+        <v>6050</v>
       </c>
       <c r="C392" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="D392">
         <v>0</v>
-      </c>
-      <c r="F392">
-        <v>1</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.2">
@@ -9546,10 +9541,10 @@
         <v>119</v>
       </c>
       <c r="B393">
-        <v>6050</v>
+        <v>6051</v>
       </c>
       <c r="C393" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="D393">
         <v>0</v>
@@ -9560,10 +9555,10 @@
         <v>119</v>
       </c>
       <c r="B394">
-        <v>6051</v>
+        <v>6052</v>
       </c>
       <c r="C394" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D394">
         <v>0</v>
@@ -9574,10 +9569,10 @@
         <v>119</v>
       </c>
       <c r="B395">
-        <v>6052</v>
+        <v>6053</v>
       </c>
       <c r="C395" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D395">
         <v>0</v>
@@ -9588,10 +9583,10 @@
         <v>119</v>
       </c>
       <c r="B396">
-        <v>6053</v>
+        <v>6054</v>
       </c>
       <c r="C396" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D396">
         <v>0</v>
@@ -9602,10 +9597,10 @@
         <v>119</v>
       </c>
       <c r="B397">
-        <v>6054</v>
+        <v>6055</v>
       </c>
       <c r="C397" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D397">
         <v>0</v>
@@ -9616,10 +9611,10 @@
         <v>119</v>
       </c>
       <c r="B398">
-        <v>6055</v>
+        <v>6056</v>
       </c>
       <c r="C398" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="D398">
         <v>0</v>
@@ -9630,10 +9625,10 @@
         <v>119</v>
       </c>
       <c r="B399">
-        <v>6056</v>
+        <v>6057</v>
       </c>
       <c r="C399" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D399">
         <v>0</v>
@@ -9644,10 +9639,10 @@
         <v>119</v>
       </c>
       <c r="B400">
-        <v>6057</v>
+        <v>6058</v>
       </c>
       <c r="C400" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D400">
         <v>0</v>
@@ -9658,10 +9653,10 @@
         <v>119</v>
       </c>
       <c r="B401">
-        <v>6058</v>
+        <v>6059</v>
       </c>
       <c r="C401" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D401">
         <v>0</v>
@@ -9672,10 +9667,10 @@
         <v>119</v>
       </c>
       <c r="B402">
-        <v>6059</v>
+        <v>6060</v>
       </c>
       <c r="C402" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D402">
         <v>0</v>
@@ -9686,10 +9681,10 @@
         <v>119</v>
       </c>
       <c r="B403">
-        <v>6060</v>
+        <v>6061</v>
       </c>
       <c r="C403" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D403">
         <v>0</v>
@@ -9700,10 +9695,10 @@
         <v>119</v>
       </c>
       <c r="B404">
-        <v>6061</v>
+        <v>6062</v>
       </c>
       <c r="C404" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D404">
         <v>0</v>
@@ -9714,51 +9709,37 @@
         <v>119</v>
       </c>
       <c r="B405">
-        <v>6062</v>
+        <v>6063</v>
       </c>
       <c r="C405" t="s">
-        <v>377</v>
+        <v>237</v>
       </c>
       <c r="D405">
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A406" t="s">
-        <v>119</v>
-      </c>
-      <c r="B406">
-        <v>6063</v>
-      </c>
-      <c r="C406" t="s">
-        <v>237</v>
-      </c>
-      <c r="D406">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O406" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="E2:H204 E216:E223">
+  <autoFilter ref="A1:O405" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="E215:E222 E2:H203">
     <cfRule type="cellIs" dxfId="2" priority="2" operator="between">
       <formula>2013</formula>
       <formula>2019</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:J244">
+  <conditionalFormatting sqref="I2:J243">
     <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I251:J251">
+  <conditionalFormatting sqref="I250:J250">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="L87" r:id="rId1" xr:uid="{C89C2450-1FD8-7143-9E0C-B19AE7020F0A}"/>
-    <hyperlink ref="L88" r:id="rId2" xr:uid="{F7A71DE7-D94B-4541-95D4-B9358594055B}"/>
-    <hyperlink ref="L204" r:id="rId3" xr:uid="{8C7E05FE-BB72-744A-87CF-185D040C290A}"/>
+    <hyperlink ref="L86" r:id="rId1" xr:uid="{C89C2450-1FD8-7143-9E0C-B19AE7020F0A}"/>
+    <hyperlink ref="L87" r:id="rId2" xr:uid="{F7A71DE7-D94B-4541-95D4-B9358594055B}"/>
+    <hyperlink ref="L203" r:id="rId3" xr:uid="{8C7E05FE-BB72-744A-87CF-185D040C290A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
